--- a/buildplan_generator/output/25-079 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-079 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,20 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-078, 25-002, 25-036, 25-096, 25-097</t>
+          <t>25-078, 25-077, 25-083, 23-055, 25-055</t>
         </is>
       </c>
     </row>
@@ -635,17 +628,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +713,8 @@
       <c r="E9" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>3</v>
+      <c r="F9" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.5</t>
+          <t>ratio=1.16 (0.67-2.20)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +750,8 @@
       <c r="E10" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>4</v>
+      <c r="F10" s="9" t="n">
+        <v>7.8</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>2.0-14.0</t>
+          <t>ratio=0.78 (0.35-2.31)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -813,8 +804,8 @@
       <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>6</v>
+      <c r="F12" s="9" t="n">
+        <v>2.8</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -823,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>1.0-10.5</t>
+          <t>ratio=1.42 (0.50-2.44)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -850,8 +841,8 @@
       <c r="E13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>4</v>
+      <c r="F13" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -860,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>2.0-6.5</t>
+          <t>ratio=0.92 (0.75-1.55)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -904,8 +895,8 @@
       <c r="E15" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>3.5</v>
+      <c r="F15" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -914,7 +905,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=1.00 (0.62-1.38)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -958,8 +949,8 @@
       <c r="E17" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>1</v>
+      <c r="F17" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -968,7 +959,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1010,17 +1001,15 @@
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
-      <c r="F19" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1047,8 +1036,8 @@
       <c r="E20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>3</v>
+      <c r="F20" s="9" t="n">
+        <v>1.1</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1057,7 +1046,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.14 (1.00-5.00)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1084,8 +1073,8 @@
       <c r="E21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>1</v>
+      <c r="F21" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1094,7 +1083,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.25 (0.64-1.83)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1121,8 +1110,8 @@
       <c r="E22" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>2</v>
+      <c r="F22" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1131,7 +1120,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=0.60 (0.29-1.05)</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1175,17 +1164,17 @@
       <c r="E24" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>1.2</v>
+      <c r="F24" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1212,17 +1201,17 @@
       <c r="E25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1249,17 +1238,17 @@
       <c r="E26" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="11" t="n">
-        <v>2.5</v>
+      <c r="F26" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>2.5-2.5</t>
+          <t>ratio=1.00 (1.00-1.25)</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1304,12 +1293,12 @@
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1336,8 +1325,8 @@
       <c r="E29" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>4</v>
+      <c r="F29" s="9" t="n">
+        <v>2.6</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1346,7 +1335,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>3.0-8.5</t>
+          <t>ratio=0.66 (0.50-0.92)</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1373,8 +1362,8 @@
       <c r="E30" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>1</v>
+      <c r="F30" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1383,7 +1372,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>1.0-6.5</t>
+          <t>ratio=1.00 (0.81-1.00)</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1408,17 +1397,15 @@
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
-      <c r="F31" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1445,7 +1432,7 @@
       <c r="E32" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="9" t="n">
         <v>4</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -1455,7 +1442,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=1.00 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1482,8 +1469,8 @@
       <c r="E33" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>1</v>
+      <c r="F33" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1492,7 +1479,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>0.5-2.0</t>
+          <t>ratio=2.19 (0.50-2.50)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1536,8 +1523,8 @@
       <c r="E35" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>6.5</v>
+      <c r="F35" s="9" t="n">
+        <v>4.9</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1546,7 +1533,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>5.0-8.5</t>
+          <t>ratio=0.99 (0.62-1.10)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1573,8 +1560,8 @@
       <c r="E36" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>5</v>
+      <c r="F36" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1583,7 +1570,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>2.0-14.0</t>
+          <t>ratio=1.50 (0.33-1.75)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1610,8 +1597,8 @@
       <c r="E37" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>9</v>
+      <c r="F37" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1620,7 +1607,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>3.0-27.5</t>
+          <t>ratio=0.20 (0.20-1.83)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1647,7 +1634,7 @@
       <c r="E38" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -1657,7 +1644,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1701,17 +1688,17 @@
       <c r="E40" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>0.5</v>
+      <c r="F40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>0.5-0.5</t>
+          <t>wc_ratio=0.96</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1736,17 +1723,15 @@
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
-      <c r="F41" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1774,12 +1759,12 @@
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1823,8 +1808,8 @@
       <c r="E44" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>2</v>
+      <c r="F44" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1833,7 +1818,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1860,8 +1845,8 @@
       <c r="E45" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>10.8</v>
+      <c r="F45" s="9" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1870,7 +1855,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>3.0-34.5</t>
+          <t>ratio=1.62 (0.77-5.00)</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1898,12 +1883,12 @@
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1931,12 +1916,12 @@
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1963,8 +1948,8 @@
       <c r="E48" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>6</v>
+      <c r="F48" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1973,7 +1958,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>4.0-24.5</t>
+          <t>ratio=1.40 (0.25-4.90)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2001,12 +1986,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2051,12 +2036,12 @@
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2070,7 +2055,7 @@
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>89</v>
+        <v>91.5</v>
       </c>
     </row>
   </sheetData>
@@ -2138,7 +2123,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-078, 25-002, 25-036, 25-096, 25-097</t>
+          <t>25-078, 25-077, 25-083, 23-055, 25-055</t>
         </is>
       </c>
     </row>
@@ -3360,28 +3345,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-002</t>
+          <t>25-077</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-036</t>
+          <t>25-083</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-096</t>
+          <t>23-055</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-097</t>
+          <t>25-055</t>
         </is>
       </c>
     </row>
@@ -3436,23 +3421,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3470,19 +3451,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>25-002, 25-036, 25-078, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3496,7 +3473,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>8.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3505,12 +3482,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.0-3.5</t>
+          <t>ratio=1.16 (0.67-2.20)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-083, 25-077, 25-055, 23-055</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3503,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3535,12 +3512,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.0-14.0</t>
+          <t>ratio=0.78 (0.35-2.31)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3533,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3565,12 +3542,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.0-10.5</t>
+          <t>ratio=1.42 (0.50-2.44)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3563,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3595,12 +3572,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.0-6.5</t>
+          <t>ratio=0.92 (0.75-1.55)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-083, 25-077, 25-055</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3593,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3625,12 +3602,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=1.00 (0.62-1.38)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-002</t>
+          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3623,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3655,12 +3632,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-083, 25-055, 23-055</t>
         </is>
       </c>
     </row>
@@ -3676,23 +3653,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3706,7 +3679,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3715,12 +3688,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.14 (1.00-5.00)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078</t>
+          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3709,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3745,12 +3718,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.25 (0.64-1.83)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078</t>
+          <t>25-083, 25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3739,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3775,12 +3748,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=0.60 (0.29-1.05)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078</t>
+          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
         </is>
       </c>
     </row>
@@ -3796,23 +3769,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3826,21 +3795,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036</t>
+          <t>25-083, 25-078, 25-077</t>
         </is>
       </c>
     </row>
@@ -3860,17 +3829,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078</t>
+          <t>25-083, 25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -3886,21 +3855,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.5-2.5</t>
+          <t>ratio=1.00 (1.00-1.25)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078</t>
+          <t>25-083, 25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -3920,19 +3889,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>25-078, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3946,7 +3911,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,12 +3920,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.0-8.5</t>
+          <t>ratio=0.66 (0.50-0.92)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-083, 25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3941,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,12 +3950,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.0-6.5</t>
+          <t>ratio=1.00 (0.81-1.00)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-078, 25-036, 25-002</t>
+          <t>25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -4006,23 +3971,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4045,12 +4006,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=1.00 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078</t>
+          <t>25-083, 25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4027,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4075,12 +4036,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.5-2.0</t>
+          <t>ratio=2.19 (0.50-2.50)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-083, 25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4057,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4105,12 +4066,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5.0-8.5</t>
+          <t>ratio=0.99 (0.62-1.10)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-002</t>
+          <t>25-083, 25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4087,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4135,12 +4096,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.0-14.0</t>
+          <t>ratio=1.50 (0.33-1.75)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-078, 25-036, 25-002</t>
+          <t>25-083, 25-078, 25-077</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4117,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4165,12 +4126,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.0-27.5</t>
+          <t>ratio=0.20 (0.20-1.83)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-078, 25-036, 25-002</t>
+          <t>25-083, 25-078, 25-077</t>
         </is>
       </c>
     </row>
@@ -4195,12 +4156,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -4216,21 +4177,21 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.5-0.5</t>
+          <t>wc_ratio=0.96</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -4246,23 +4207,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4280,19 +4237,15 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>25-078, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4306,7 +4259,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4315,12 +4268,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4289,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4345,12 +4298,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.0-34.5</t>
+          <t>ratio=1.62 (0.77-5.00)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-083, 25-078, 25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -4370,19 +4323,15 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>25-002, 25-036, 25-078, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4400,19 +4349,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>25-078, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4426,7 +4371,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4435,12 +4380,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.0-24.5</t>
+          <t>ratio=1.40 (0.25-4.90)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-078, 25-036, 25-002</t>
+          <t>25-083, 25-078, 25-077</t>
         </is>
       </c>
     </row>
@@ -4460,19 +4405,15 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>25-002, 25-036, 25-078, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4490,19 +4431,15 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>25-002, 25-036, 25-078, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/buildplan_generator/output/25-079 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-079 GENERATED BUILD PLAN.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-078, 25-077, 25-083, 23-055, 25-055</t>
+          <t>25-078, 25-077, 23-055, 25-083, 25-055</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-078, 25-077, 25-083, 23-055, 25-055</t>
+          <t>25-078, 25-077, 23-055, 25-083, 25-055</t>
         </is>
       </c>
     </row>
@@ -3352,14 +3352,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-083</t>
+          <t>23-055</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-055</t>
+          <t>25-083</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-079 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-079 GENERATED BUILD PLAN.xlsx
@@ -631,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -664,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -714,7 +714,7 @@
         <v>7</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.16 (0.67-2.20)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.35-2.31)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -805,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.42 (0.50-2.44)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -842,7 +842,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.75-1.55)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -896,7 +896,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.38)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -949,17 +949,17 @@
       <c r="E17" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1004,12 +1004,12 @@
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.14 (1.00-5.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1074,7 +1074,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.64-1.83)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1111,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.60 (0.29-1.05)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1165,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1239,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.25)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1293,12 +1293,12 @@
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1326,7 +1326,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.66 (0.50-0.92)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1363,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.81-1.00)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1400,12 +1400,12 @@
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1433,7 +1433,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.50)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1469,17 +1469,17 @@
       <c r="E33" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="9" t="n">
-        <v>2.2</v>
+      <c r="F33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.19 (0.50-2.50)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1524,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>4.9</v>
+        <v>7.3</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.99 (0.62-1.10)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1561,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.33-1.75)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1598,7 +1598,7 @@
         <v>15</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>3</v>
+        <v>7.3</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.20 (0.20-1.83)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1688,17 +1688,17 @@
       <c r="E40" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>1</v>
+      <c r="F40" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.96</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1726,12 +1726,12 @@
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1759,12 +1759,12 @@
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1846,7 +1846,7 @@
         <v>6</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.62 (0.77-5.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1883,12 +1883,12 @@
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1916,12 +1916,12 @@
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1949,7 +1949,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>7</v>
+        <v>18.4</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.40 (0.25-4.90)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -1986,12 +1986,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2036,12 +2036,12 @@
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>91.5</v>
+        <v>89.3</v>
       </c>
     </row>
   </sheetData>
@@ -3425,15 +3425,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3451,15 +3455,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3473,7 +3481,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3482,12 +3490,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.16 (0.67-2.20)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-083, 25-077, 25-055, 23-055</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3511,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3512,12 +3520,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.35-2.31)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3541,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3542,12 +3550,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.42 (0.50-2.44)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3571,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3572,12 +3580,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.75-1.55)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-083, 25-077, 25-055</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3601,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3602,12 +3610,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.38)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -3627,17 +3635,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 23-055</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -3657,15 +3665,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3688,12 +3700,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.14 (1.00-5.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3721,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3718,12 +3730,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.64-1.83)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 23-055</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3751,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3748,12 +3760,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=0.60 (0.29-1.05)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 25-055, 23-055</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -3773,15 +3785,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3795,7 +3811,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3804,12 +3820,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3841,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3834,12 +3850,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 23-055</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3871,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3864,12 +3880,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.25)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 23-055</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -3889,15 +3905,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3911,7 +3931,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,12 +3940,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=0.66 (0.50-0.92)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3961,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3950,12 +3970,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.81-1.00)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-078, 25-077, 23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -3975,15 +3995,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3997,7 +4021,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4006,12 +4030,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.50)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -4027,21 +4051,21 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=2.19 (0.50-2.50)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 23-055</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4081,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.9</v>
+        <v>7.3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,12 +4090,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=0.99 (0.62-1.10)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4111,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4096,12 +4120,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.33-1.75)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4141,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>7.3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4126,12 +4150,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=0.20 (0.20-1.83)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4171,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4156,12 +4180,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-078, 25-077, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4177,21 +4201,21 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>wc_ratio=0.96</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4211,15 +4235,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4237,15 +4265,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4259,7 +4291,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4268,12 +4300,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-078, 25-077, 23-055</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4321,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9.699999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4298,12 +4330,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=1.62 (0.77-5.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077, 23-055</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4323,15 +4355,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4349,15 +4385,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4371,7 +4411,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>18.4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4380,12 +4420,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=1.40 (0.25-4.90)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-083, 25-078, 25-077</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4405,15 +4445,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4431,15 +4475,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/buildplan_generator/output/25-079 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-079 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>7</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:9h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:9h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -805,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -842,7 +842,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -896,7 +896,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1074,7 +1074,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1111,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1165,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1239,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1326,7 +1326,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1363,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1433,7 +1433,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1524,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1561,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1598,7 +1598,7 @@
         <v>15</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1846,7 +1846,7 @@
         <v>6</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1949,7 +1949,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>18.4</v>
+        <v>17.6</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>89.3</v>
+        <v>88.5</v>
       </c>
     </row>
   </sheetData>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:9h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:9h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>18.4</v>
+        <v>17.6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
